--- a/data/output/workbook/2026-07-04.xlsx
+++ b/data/output/workbook/2026-07-04.xlsx
@@ -370,7 +370,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10048875"/>
+    <ext cx="10125075" cy="10439400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -400,7 +400,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10525125"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -460,7 +460,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9801225"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10287000"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04 06:12</t>
+          <t>2026-07-04 08:12</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,875 +1174,875 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>Toronto Blue Jays offense vs Seattle Mariners defense</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F64" s="30" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G64" s="30" t="inlineStr">
+      <c r="G67" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H64" s="30" t="inlineStr">
+      <c r="H67" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I64" s="30" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J64" s="30" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K64" s="30" t="inlineStr">
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L64" s="30" t="inlineStr">
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M64" s="30" t="inlineStr">
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N64" s="30" t="inlineStr">
+      <c r="N67" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O64" s="30" t="inlineStr">
+      <c r="O67" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P64" s="30" t="inlineStr">
+      <c r="P67" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q64" s="30" t="inlineStr">
+      <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B65" s="32" t="n">
-        <v>4.068</v>
-      </c>
-      <c r="C65" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F65" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G65" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>4.057</v>
-      </c>
-      <c r="Q65" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.468</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>7.979</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>7.298</v>
+        <v>4.068</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.2</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.3</v>
       </c>
       <c r="O68" s="32" t="n">
-        <v>10.25</v>
+        <v>4.033</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>8.333</v>
+        <v>4.057</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>7.979</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B69" s="32" t="n">
+      <c r="B72" s="32" t="n">
         <v>0.438</v>
       </c>
-      <c r="C69" s="32" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D69" s="32" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F69" s="32" t="n">
+      <c r="F72" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G69" s="32" t="n">
+      <c r="G72" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H69" s="36" t="inlineStr">
+      <c r="H72" s="36" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K69" s="32" t="n">
+      <c r="K72" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L69" s="32" t="n">
+      <c r="L72" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M69" s="32" t="n">
+      <c r="M72" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N69" s="32" t="n">
+      <c r="N72" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O69" s="32" t="n">
+      <c r="O72" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P69" s="32" t="n">
+      <c r="P72" s="32" t="n">
         <v>0.419</v>
       </c>
-      <c r="Q69" s="34" t="inlineStr">
+      <c r="Q72" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Seattle Mariners offense vs Toronto Blue Jays defense</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F72" s="30" t="inlineStr">
+      <c r="F75" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G72" s="30" t="inlineStr">
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H72" s="30" t="inlineStr">
+      <c r="H75" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I72" s="30" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J72" s="30" t="inlineStr">
+      <c r="J75" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K72" s="30" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L72" s="30" t="inlineStr">
+      <c r="L75" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M72" s="30" t="inlineStr">
+      <c r="M75" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N72" s="30" t="inlineStr">
+      <c r="N75" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O72" s="30" t="inlineStr">
+      <c r="O75" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P72" s="30" t="inlineStr">
+      <c r="P75" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q72" s="30" t="inlineStr">
+      <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>3.897</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>4.432</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.894</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>1.312</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>8.646000000000001</v>
+        <v>3.897</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.667</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.65</v>
       </c>
       <c r="O76" s="32" t="n">
-        <v>6.25</v>
+        <v>5.067</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>9.489000000000001</v>
+        <v>4.432</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>7.894</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>9.489000000000001</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B77" s="32" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.473</v>
       </c>
-      <c r="C77" s="32" t="n">
+      <c r="C80" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D77" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E77" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F77" s="32" t="n">
+      <c r="F80" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G77" s="32" t="n">
+      <c r="G80" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="35" t="inlineStr">
+      <c r="H80" s="35" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="33" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="K77" s="32" t="n">
+      <c r="K80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L77" s="32" t="n">
+      <c r="L80" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M77" s="32" t="n">
+      <c r="M80" s="32" t="n">
         <v>1.067</v>
       </c>
-      <c r="N77" s="32" t="n">
+      <c r="N80" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O77" s="32" t="n">
+      <c r="O80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P77" s="32" t="n">
+      <c r="P80" s="32" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="Q77" s="34" t="inlineStr">
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2061,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2078,170 +2078,245 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Cincinnati Reds defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.558</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.558</v>
+        <v>8.208</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>9.5</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.1</v>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.6</v>
+        <v>8.333</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.68</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.208</v>
+        <v>1.271</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -2295,28 +2370,28 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>8.333</v>
+        <v>1.667</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.106</v>
+        <v>1.383</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.271</v>
+        <v>8.917</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -2370,319 +2445,319 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>1.667</v>
+        <v>7.667</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.383</v>
+        <v>7.404</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.917</v>
+        <v>0.5</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.733</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.3</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>7.667</v>
+        <v>0.533</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.404</v>
+        <v>0.527</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Baltimore Orioles defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>3.987</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>3.987</v>
+        <v>7.404</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>6.667</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>4.1</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.267</v>
+        <v>6.5</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.818</v>
+        <v>8.833</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.404</v>
+        <v>1.213</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>6.667</v>
+        <v>1.667</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -2736,28 +2811,28 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.833</v>
+        <v>1.062</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.213</v>
+        <v>9.532</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1.667</v>
+        <v>12</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -2811,146 +2886,71 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>8</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>9.532</v>
+        <v>0.554</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.9</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8</v>
+        <v>0.487</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6605,7 +6605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6622,324 +6622,174 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>San Francisco Giants offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="G67" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H67" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N65" s="30" t="inlineStr">
+      <c r="N67" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O65" s="30" t="inlineStr">
+      <c r="O67" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="P67" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>4.114</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>5.641</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>9.239000000000001</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>0.978</v>
+        <v>4.114</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.733</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>5.65</v>
       </c>
       <c r="O68" s="32" t="n">
-        <v>1.333</v>
+        <v>6.5</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>1.24</v>
+        <v>5.641</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>7.587</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>9.5</v>
+        <v>12.25</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -6993,394 +6843,394 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>7.333</v>
+        <v>14</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>7.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.587</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
+      <c r="B72" s="32" t="n">
         <v>0.347</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="E70" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="F70" s="32" t="n">
+      <c r="F72" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G72" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="35" t="inlineStr">
+      <c r="H72" s="35" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K70" s="32" t="n">
+      <c r="K72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L70" s="32" t="n">
+      <c r="L72" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M70" s="32" t="n">
+      <c r="M72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N70" s="32" t="n">
+      <c r="N72" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="O70" s="32" t="n">
+      <c r="O72" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P70" s="32" t="n">
+      <c r="P72" s="32" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="Q70" s="34" t="inlineStr">
+      <c r="Q72" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs San Francisco Giants defense</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F75" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G73" s="30" t="inlineStr">
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H73" s="30" t="inlineStr">
+      <c r="H75" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I73" s="30" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J73" s="30" t="inlineStr">
+      <c r="J75" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K73" s="30" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L73" s="30" t="inlineStr">
+      <c r="L75" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M73" s="30" t="inlineStr">
+      <c r="M75" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N73" s="30" t="inlineStr">
+      <c r="N75" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O73" s="30" t="inlineStr">
+      <c r="O75" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P73" s="30" t="inlineStr">
+      <c r="P75" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q73" s="30" t="inlineStr">
+      <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>6.233</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>6.267</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>4.975</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>8.651999999999999</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>0.92</v>
+        <v>4.91</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6.233</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.75</v>
       </c>
       <c r="O76" s="32" t="n">
-        <v>0.75</v>
+        <v>5.1</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>0.978</v>
+        <v>4.975</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>8.92</v>
+        <v>8.32</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>9.667</v>
+        <v>10.667</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -7434,75 +7284,225 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>7.25</v>
+        <v>13.5</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.173999999999999</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B78" s="32" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.506</v>
       </c>
-      <c r="C78" s="32" t="n">
+      <c r="C80" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D78" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E78" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F78" s="32" t="n">
+      <c r="F80" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G78" s="32" t="n">
+      <c r="G80" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H78" s="33" t="inlineStr">
+      <c r="H80" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J78" s="35" t="inlineStr">
+      <c r="J80" s="35" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="K78" s="32" t="n">
+      <c r="K80" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="L78" s="32" t="n">
+      <c r="L80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M78" s="32" t="n">
+      <c r="M80" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N78" s="32" t="n">
+      <c r="N80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O78" s="32" t="n">
+      <c r="O80" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P78" s="32" t="n">
+      <c r="P80" s="32" t="n">
         <v>0.569</v>
       </c>
-      <c r="Q78" s="34" t="inlineStr">
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7599,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -7937,17 +7937,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6167317073170732</v>
+        <v>0.6083307692307692</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>105</v>
+        <v>-108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8007,13 +8007,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6178490566037736</v>
+        <v>0.6178394366197183</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8049,37 +8049,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.46</v>
+        <v>0.5744470588235294</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>117</v>
+        <v>-135</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8115,37 +8115,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5744268292682927</v>
+        <v>0.4611885245901639</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-135</v>
+        <v>117</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-105</v>
+        <v>144</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5082159624413146</v>
+        <v>0.4314</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-103</v>
+        <v>132</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.43208</v>
+        <v>0.5104265402843601</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>131</v>
+        <v>-104</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8379,7 +8379,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8403,13 +8403,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4846396396396397</v>
+        <v>0.4126538461538461</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8445,7 +8445,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4115769230769231</v>
+        <v>0.4827027027027028</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8516,32 +8516,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4347950819672131</v>
+        <v>0.42556</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6158365145228215</v>
+        <v>0.4383333333333334</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-160</v>
+        <v>128</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-141</v>
+        <v>140</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4734234234234235</v>
+        <v>0.4721171171171172</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>122</v>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8780,32 +8780,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4255327868852459</v>
+        <v>0.6188878542510122</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>135</v>
+        <v>-162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>144</v>
+        <v>-147</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8997,13 +8997,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5880540772532189</v>
+        <v>0.586148275862069</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.51095</v>
+        <v>0.5838300429184549</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-104</v>
+        <v>-140</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>-133</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9105,37 +9105,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4385407725321889</v>
+        <v>0.51095</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>128</v>
+        <v>-104</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5615297297297297</v>
+        <v>0.4385407725321889</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-128</v>
+        <v>128</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-122</v>
+        <v>133</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9234,9 +9234,75 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.5615297297297297</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.2% (fair -128). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J27">
+  <conditionalFormatting sqref="J5:J28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9402,13 +9468,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6158365145228215</v>
+        <v>0.6188878542510122</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-160</v>
+        <v>-162</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-141</v>
+        <v>-147</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9432,7 +9498,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9468,10 +9534,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3841393442622951</v>
+        <v>0.3811065573770492</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>144</v>
@@ -9498,7 +9564,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9534,13 +9600,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5726</v>
+        <v>0.5728</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-134</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9600,7 +9666,7 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4274</v>
+        <v>0.4272</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>134</v>
@@ -9666,10 +9732,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.43208</v>
+        <v>0.4314</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>150</v>
@@ -9696,7 +9762,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9732,13 +9798,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.56796</v>
+        <v>0.5685691056910569</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-150</v>
+        <v>-146</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9762,7 +9828,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9794,17 +9860,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4236</v>
+        <v>0.4234</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>136</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9828,7 +9894,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9860,17 +9926,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5764</v>
+        <v>0.5766</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9894,7 +9960,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9930,13 +9996,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3832599118942731</v>
+        <v>0.4161739130434783</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9960,7 +10026,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9996,13 +10062,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6167317073170732</v>
+        <v>0.5838300429184549</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-161</v>
+        <v>-140</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>105</v>
+        <v>-133</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10026,7 +10092,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10062,10 +10128,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5109408866995073</v>
+        <v>0.5117527093596059</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-103</v>
@@ -10092,7 +10158,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10128,13 +10194,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4890196078431372</v>
+        <v>0.4882439024390244</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10158,7 +10224,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10326,13 +10392,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4097570850202429</v>
+        <v>0.4116666666666666</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10356,7 +10422,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10392,13 +10458,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5902200000000001</v>
+        <v>0.588357085020243</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10422,7 +10488,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10590,13 +10656,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4255327868852459</v>
+        <v>0.42556</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>135</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10656,13 +10722,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5744268292682927</v>
+        <v>0.5744470588235294</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-135</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10722,13 +10788,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5082159624413146</v>
+        <v>0.5104265402843601</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10752,7 +10818,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10788,13 +10854,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4917887323943662</v>
+        <v>0.4895773584905661</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10818,7 +10884,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10850,17 +10916,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4351</v>
+        <v>0.5108</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>130</v>
+        <v>-104</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10884,7 +10950,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10916,17 +10982,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5649</v>
+        <v>0.4892</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-130</v>
+        <v>104</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10950,7 +11016,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11118,7 +11184,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.50135</v>
+        <v>0.5021</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>-101</v>
@@ -11148,7 +11214,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11184,7 +11250,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.49865</v>
+        <v>0.4979</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>101</v>
@@ -11214,7 +11280,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11250,13 +11316,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6257</v>
+        <v>0.623</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-167</v>
+        <v>-165</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11280,7 +11346,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -167). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11316,10 +11382,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3743</v>
+        <v>0.377</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>107</v>
@@ -11346,7 +11412,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +167). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11510,7 +11576,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
@@ -11520,7 +11586,7 @@
         <v>128</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11576,7 +11642,7 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
@@ -11712,13 +11778,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6178490566037736</v>
+        <v>0.6178394366197183</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11778,13 +11844,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4347950819672131</v>
+        <v>0.4383333333333334</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11808,7 +11874,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11844,13 +11910,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5652</v>
+        <v>0.5616628099173554</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-144</v>
+        <v>-142</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11874,7 +11940,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11982,7 +12048,7 @@
         <v>156</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12042,13 +12108,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4060833333333334</v>
+        <v>0.3916599190283401</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12072,7 +12138,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12108,13 +12174,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5939409836065573</v>
+        <v>0.6083307692307692</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-146</v>
+        <v>-155</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-144</v>
+        <v>-108</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12138,7 +12204,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12174,10 +12240,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4115769230769231</v>
+        <v>0.4126538461538461</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>160</v>
@@ -12204,7 +12270,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12240,13 +12306,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5884557251908397</v>
+        <v>0.5873177606177606</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-162</v>
+        <v>-159</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12270,7 +12336,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12378,7 +12444,7 @@
         <v>-182</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12438,13 +12504,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4119827586206896</v>
+        <v>0.4138695652173913</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12468,7 +12534,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12504,13 +12570,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5880540772532189</v>
+        <v>0.586148275862069</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12534,7 +12600,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13088,7 +13154,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
@@ -13098,7 +13164,7 @@
         <v>-104</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13154,7 +13220,7 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
@@ -13608,10 +13674,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4846396396396397</v>
+        <v>0.4827027027027028</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>122</v>
@@ -13638,7 +13704,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13674,10 +13740,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5153391705069124</v>
+        <v>0.5172801843317972</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-117</v>
@@ -13704,7 +13770,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14004,7 +14070,7 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.46</v>
+        <v>0.4611885245901639</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>117</v>
@@ -14034,7 +14100,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14070,7 +14136,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5399914163090128</v>
+        <v>0.5388497854077253</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>-117</v>
@@ -14100,7 +14166,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14532,13 +14598,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.526537558685446</v>
+        <v>0.5278767441860466</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14562,7 +14628,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14598,10 +14664,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4734234234234235</v>
+        <v>0.4721171171171172</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>122</v>
@@ -14628,7 +14694,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -17015,7 +17081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17032,324 +17098,174 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs New York Yankees defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.776</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.933</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>3.744</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.609</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.061</v>
+        <v>4.776</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.3</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.65</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>2</v>
+        <v>4.633</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>0.913</v>
+        <v>3.744</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.939</v>
+        <v>7.776</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>8</v>
+        <v>8.667</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -17403,394 +17319,394 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>9.667</v>
+        <v>10.667</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.435</v>
+        <v>7.609</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.435</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.833</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="35" t="inlineStr">
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.479</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>New York Yankees offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.744</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>5.767</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>5.132</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>8.109</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.413</v>
+        <v>4.744</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.467</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>5.6</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>1.667</v>
+        <v>5.767</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.918</v>
+        <v>5.132</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>9.130000000000001</v>
+        <v>8.109</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>9.667</v>
+        <v>8.333</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -17844,71 +17760,221 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>11.667</v>
+        <v>9</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.63</v>
+        <v>1.413</v>
       </c>
       <c r="C81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C83" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D83" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H81" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.605</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-04.xlsx
+++ b/data/output/workbook/2026-07-04.xlsx
@@ -340,7 +340,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10810875"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04 08:12</t>
+          <t>2026-07-04 10:33</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7743,13 +7743,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6968148148148148</v>
+        <v>0.6967985611510791</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-230</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7790,32 +7790,32 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5524892703862662</v>
+        <v>0.6219711538461539</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-123</v>
+        <v>-165</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7851,7 +7851,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5735135135135137</v>
+        <v>0.5524892703862662</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-134</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -134). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7917,37 +7917,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6083307692307692</v>
+        <v>0.5735135135135137</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-155</v>
+        <v>-134</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 57.4% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8003,17 +8003,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6178394366197183</v>
+        <v>0.6083596059113301</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-113</v>
+        <v>-103</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8069,17 +8069,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5744470588235294</v>
+        <v>0.6178373831775701</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-135</v>
+        <v>-162</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-104</v>
+        <v>-114</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8115,37 +8115,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4611885245901639</v>
+        <v>0.5779647058823528</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>117</v>
+        <v>-137</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8186,12 +8186,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8201,17 +8201,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.46</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-120</v>
+        <v>117</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8247,17 +8247,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4314</v>
+        <v>0.5464</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>132</v>
+        <v>-120</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8337,13 +8337,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5104265402843601</v>
+        <v>0.5025806451612903</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8379,7 +8379,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8403,13 +8403,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4126538461538461</v>
+        <v>0.4834684684684685</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8445,7 +8445,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4827027027027028</v>
+        <v>0.4134883720930232</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8516,32 +8516,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.42556</v>
+        <v>0.4361065573770492</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4383333333333334</v>
+        <v>0.4347950819672131</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4721171171171172</v>
+        <v>0.4707207207207207</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>112</v>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8733,13 +8733,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5128921568627451</v>
+        <v>0.51955</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8795,17 +8795,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6188878542510122</v>
+        <v>0.4452789699570815</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-162</v>
+        <v>125</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-147</v>
+        <v>133</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8846,32 +8846,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4442918454935622</v>
+        <v>0.4220491803278689</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8907,37 +8907,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5356903846153847</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-115</v>
+        <v>-106</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.586148275862069</v>
+        <v>0.5337692307692308</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-142</v>
+        <v>-114</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-132</v>
+        <v>-108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5838300429184549</v>
+        <v>0.4211065573770492</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-140</v>
+        <v>137</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-133</v>
+        <v>144</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9105,37 +9105,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.51095</v>
+        <v>0.552110599078341</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-104</v>
+        <v>-123</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>-117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9171,37 +9171,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4385407725321889</v>
+        <v>0.5838300429184549</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>128</v>
+        <v>-140</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>133</v>
+        <v>-133</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9237,17 +9237,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5615297297297297</v>
+        <v>0.40904</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-128</v>
+        <v>144</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-122</v>
+        <v>150</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9300,9 +9300,75 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.592472268907563</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-138</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.2% (fair -145). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J28">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9324,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9468,13 +9534,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6188878542510122</v>
+        <v>0.5788918032786885</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-162</v>
+        <v>-137</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-147</v>
+        <v>-144</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9498,7 +9564,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9534,10 +9600,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3811065573770492</v>
+        <v>0.4211065573770492</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>144</v>
@@ -9564,7 +9630,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9600,13 +9666,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5728</v>
+        <v>0.4566</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-134</v>
+        <v>119</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9630,7 +9696,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9666,13 +9732,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4272</v>
+        <v>0.5434</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>134</v>
+        <v>-119</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9696,7 +9762,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9713,32 +9779,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4314</v>
+        <v>0.5337692307692308</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>132</v>
+        <v>-114</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>150</v>
+        <v>-108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9762,7 +9828,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9779,32 +9845,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5685691056910569</v>
+        <v>0.4662254901960785</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-132</v>
+        <v>114</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-146</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9828,7 +9894,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9855,22 +9921,22 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4234</v>
+        <v>0.4361065573770492</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9894,7 +9960,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9921,22 +9987,22 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5766</v>
+        <v>0.5639016393442623</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-136</v>
+        <v>-129</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>-144</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9960,7 +10026,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9987,22 +10053,22 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4161739130434783</v>
+        <v>0.4234</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10026,7 +10092,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10053,22 +10119,22 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5838300429184549</v>
+        <v>0.5766</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-140</v>
+        <v>-136</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-133</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10092,7 +10158,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10109,32 +10175,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5117527093596059</v>
+        <v>0.4161739130434783</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-105</v>
+        <v>140</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-103</v>
+        <v>130</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10158,7 +10224,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10175,32 +10241,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4882439024390244</v>
+        <v>0.5838300429184549</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>105</v>
+        <v>-140</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>105</v>
+        <v>-133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10224,7 +10290,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10251,22 +10317,22 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5952</v>
+        <v>0.5116392156862745</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-147</v>
+        <v>-105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10290,7 +10356,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10317,22 +10383,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4048</v>
+        <v>0.4883823529411764</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10356,7 +10422,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10373,32 +10439,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4116666666666666</v>
+        <v>0.5995</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>143</v>
+        <v>-150</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10422,7 +10488,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10439,32 +10505,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.588357085020243</v>
+        <v>0.4005</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-143</v>
+        <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-147</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10488,7 +10554,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10515,22 +10581,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4890549019607843</v>
+        <v>0.40904</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>150</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10554,7 +10620,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10581,22 +10647,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.51095</v>
+        <v>0.5909901639344263</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-104</v>
+        <v>-144</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>-144</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10620,7 +10686,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10647,22 +10713,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.42556</v>
+        <v>0.4853843137254901</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>150</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10686,7 +10752,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10713,22 +10779,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5744470588235294</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-135</v>
+        <v>-106</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10752,7 +10818,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10769,32 +10835,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5104265402843601</v>
+        <v>0.4220491803278689</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-104</v>
+        <v>137</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10818,7 +10884,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10835,32 +10901,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4895773584905661</v>
+        <v>0.5779647058823528</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>104</v>
+        <v>-137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-112</v>
+        <v>-104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10884,7 +10950,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10911,22 +10977,22 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5108</v>
+        <v>0.5025806451612903</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10950,7 +11016,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10977,22 +11043,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4892</v>
+        <v>0.4974387096774193</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>112</v>
+        <v>-117</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11016,7 +11082,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11043,22 +11109,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3031851851851852</v>
+        <v>0.5108</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>230</v>
+        <v>-104</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11082,7 +11148,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 30.3% (fair +230). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11109,22 +11175,22 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6968148148148148</v>
+        <v>0.4892</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-230</v>
+        <v>104</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11148,7 +11214,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 69.7% (fair -230). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11165,7 +11231,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -11175,22 +11241,22 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Cincinnati Reds -1.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5021</v>
+        <v>0.3031851851851852</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-101</v>
+        <v>230</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11214,7 +11280,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 30.3% (fair +230). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11231,7 +11297,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -11241,22 +11307,22 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4979</v>
+        <v>0.6967985611510791</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>101</v>
+        <v>-230</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11280,7 +11346,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11307,22 +11373,22 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.623</v>
+        <v>0.5017</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-165</v>
+        <v>-101</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11346,7 +11412,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11373,22 +11439,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.377</v>
+        <v>0.4983</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11412,7 +11478,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11429,7 +11495,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -11439,22 +11505,22 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4442918454935622</v>
+        <v>0.6083</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>125</v>
+        <v>-155</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11478,7 +11544,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11495,7 +11561,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -11505,22 +11571,22 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5557404255319149</v>
+        <v>0.3917</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-125</v>
+        <v>155</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-135</v>
+        <v>106</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11544,7 +11610,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11571,22 +11637,22 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4379</v>
+        <v>0.4452789699570815</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11610,7 +11676,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11637,22 +11703,22 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5621</v>
+        <v>0.5547184549356223</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-128</v>
+        <v>-125</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11676,7 +11742,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11703,22 +11769,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians -1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3821484375</v>
+        <v>0.4379</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11742,7 +11808,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11769,22 +11835,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6178394366197183</v>
+        <v>0.5621</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-162</v>
+        <v>-128</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11808,7 +11874,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11825,32 +11891,32 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Cleveland Guardians -1.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4383333333333334</v>
+        <v>0.3821484375</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11874,7 +11940,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11891,32 +11957,32 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5616628099173554</v>
+        <v>0.6178373831775701</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-128</v>
+        <v>-162</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-142</v>
+        <v>-114</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11940,7 +12006,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11967,22 +12033,22 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.6087</v>
+        <v>0.4347950819672131</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-156</v>
+        <v>130</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12006,7 +12072,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12033,22 +12099,22 @@
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.3913</v>
+        <v>0.5652</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>156</v>
+        <v>-130</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>110</v>
+        <v>-144</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12072,7 +12138,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12099,22 +12165,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3916599190283401</v>
+        <v>0.6087</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>155</v>
+        <v>-156</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12138,7 +12204,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12165,22 +12231,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6083307692307692</v>
+        <v>0.3913</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-155</v>
+        <v>156</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12204,7 +12270,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12221,7 +12287,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -12231,22 +12297,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4126538461538461</v>
+        <v>0.3916326530612245</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12270,7 +12336,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12287,7 +12353,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -12297,22 +12363,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5873177606177606</v>
+        <v>0.6083596059113301</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-142</v>
+        <v>-155</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-159</v>
+        <v>-103</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12336,7 +12402,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12363,22 +12429,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3542</v>
+        <v>0.4134883720930232</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12402,7 +12468,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +182). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12429,22 +12495,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6457999999999999</v>
+        <v>0.5865230769230769</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-182</v>
+        <v>-142</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>115</v>
+        <v>-160</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12468,7 +12534,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12495,22 +12561,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4138695652173913</v>
+        <v>0.3542</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12534,7 +12600,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 35.4% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12561,22 +12627,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.586148275862069</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-142</v>
+        <v>-182</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-132</v>
+        <v>113</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12600,7 +12666,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 64.6% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12617,31 +12683,33 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.5046</v>
+        <v>0.3780616740088106</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H53" s="15" t="n"/>
+        <v>165</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>127</v>
+      </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
         <v/>
@@ -12664,7 +12732,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12681,31 +12749,33 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.6219711538461539</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>102</v>
-      </c>
-      <c r="H54" s="15" t="n"/>
+        <v>-165</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
         <v/>
@@ -12728,7 +12798,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12745,7 +12815,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -12760,18 +12830,16 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5898050420168067</v>
+        <v>0.5046</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-144</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-138</v>
-      </c>
+        <v>-102</v>
+      </c>
+      <c r="H55" s="15" t="n"/>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
         <v/>
@@ -12794,7 +12862,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12811,7 +12879,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
@@ -12826,18 +12894,16 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4101680672268908</v>
+        <v>0.4955</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>144</v>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>138</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H56" s="15" t="n"/>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
         <v/>
@@ -12860,7 +12926,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12887,22 +12953,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4249</v>
+        <v>0.592472268907563</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>135</v>
+        <v>-145</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>122</v>
+        <v>-138</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12926,7 +12992,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -12953,22 +13019,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.4075206611570248</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-135</v>
+        <v>145</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12992,7 +13058,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13009,32 +13075,32 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5524892703862662</v>
+        <v>0.4249</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-123</v>
+        <v>135</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13058,7 +13124,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13075,31 +13141,33 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4475</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>123</v>
-      </c>
-      <c r="H60" s="15" t="n"/>
+        <v>-135</v>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
         <v/>
@@ -13122,7 +13190,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13149,22 +13217,22 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5101</v>
+        <v>0.5524892703862662</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-104</v>
+        <v>-123</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13188,7 +13256,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13215,23 +13283,21 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4899</v>
+        <v>0.4475</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>104</v>
-      </c>
-      <c r="H62" s="15" t="n">
-        <v>108</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -13254,7 +13320,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13271,31 +13337,33 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5484</v>
+        <v>0.5101</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H63" s="15" t="n"/>
+        <v>-104</v>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>110</v>
+      </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
         <v/>
@@ -13318,7 +13386,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13335,31 +13403,33 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4516</v>
+        <v>0.4899</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="H64" s="15" t="n"/>
+        <v>104</v>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
         <v/>
@@ -13382,7 +13452,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13399,7 +13469,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -13414,14 +13484,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6928</v>
+        <v>0.5484</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-226</v>
+        <v>-121</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13446,7 +13516,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13463,7 +13533,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -13478,14 +13548,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3071</v>
+        <v>0.4516</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>226</v>
+        <v>121</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13510,7 +13580,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 30.7% (fair +226). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13527,12 +13597,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -13542,14 +13612,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.3626</v>
+        <v>0.6928</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>176</v>
+        <v>-226</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -13574,7 +13644,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +176). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13591,12 +13661,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -13606,14 +13676,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.6374</v>
+        <v>0.3071</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-176</v>
+        <v>226</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13638,7 +13708,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -176). Your call.</t>
+          <t>Model 30.7% (fair +226). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13650,17 +13720,17 @@
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -13670,18 +13740,16 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4827027027027028</v>
+        <v>0.3603</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>107</v>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
         <v/>
@@ -13704,7 +13772,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13716,17 +13784,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -13736,18 +13804,16 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5172801843317972</v>
+        <v>0.6397</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-107</v>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-117</v>
-      </c>
+        <v>-178</v>
+      </c>
+      <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
         <v/>
@@ -13770,7 +13836,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13787,12 +13853,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -13802,17 +13868,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5356903846153847</v>
+        <v>0.4834684684684685</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-115</v>
+        <v>107</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -13836,7 +13902,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13853,12 +13919,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -13868,17 +13934,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4643317972350231</v>
+        <v>0.5165253456221198</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>115</v>
+        <v>-107</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>117</v>
+        <v>-117</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13902,7 +13968,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -13919,12 +13985,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -13934,17 +14000,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.5412328638497652</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13968,7 +14034,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13985,12 +14051,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -14000,17 +14066,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.4588018433179724</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14034,7 +14100,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14051,12 +14117,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -14066,17 +14132,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4611885245901639</v>
+        <v>0.5464</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>117</v>
+        <v>-120</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14100,7 +14166,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14117,12 +14183,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -14132,17 +14198,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5388497854077253</v>
+        <v>0.4536</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-117</v>
+        <v>120</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14166,7 +14232,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14183,12 +14249,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14198,17 +14264,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4591891891891893</v>
+        <v>0.46</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14232,7 +14298,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14249,12 +14315,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14264,14 +14330,14 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5407905579399142</v>
+        <v>0.5399914163090128</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-133</v>
@@ -14298,7 +14364,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14315,12 +14381,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -14330,17 +14396,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4385407725321889</v>
+        <v>0.458963963963964</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14364,7 +14430,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14381,12 +14447,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14396,17 +14462,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5614512605042017</v>
+        <v>0.5410188841201716</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-128</v>
+        <v>-118</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14430,7 +14496,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14447,12 +14513,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14462,17 +14528,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5615297297297297</v>
+        <v>0.4378111587982833</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-128</v>
+        <v>128</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-122</v>
+        <v>133</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14496,7 +14562,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14513,12 +14579,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14528,17 +14594,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4384581497797357</v>
+        <v>0.5621470588235294</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>128</v>
+        <v>-128</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>127</v>
+        <v>-138</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14562,7 +14628,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14579,12 +14645,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -14594,17 +14660,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5278767441860466</v>
+        <v>0.5708725321888413</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-112</v>
+        <v>-133</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-115</v>
+        <v>-133</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14628,7 +14694,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14645,12 +14711,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -14660,17 +14726,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4721171171171172</v>
+        <v>0.4290987124463519</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14694,7 +14760,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14711,7 +14777,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -14726,17 +14792,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5128921568627451</v>
+        <v>0.5292674418604651</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>104</v>
+        <v>-115</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14760,7 +14826,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14777,7 +14843,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
@@ -14792,17 +14858,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4871423076923077</v>
+        <v>0.4707207207207207</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14826,7 +14892,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14843,12 +14909,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -14858,16 +14924,18 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.51955</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H87" s="15" t="n"/>
+        <v>-108</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
         <v/>
@@ -14890,7 +14958,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14907,12 +14975,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -14922,16 +14990,18 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.4804392156862745</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H88" s="15" t="n"/>
+        <v>108</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-104</v>
+      </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
         <v/>
@@ -14954,7 +15024,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -14971,7 +15041,7 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -14986,18 +15056,16 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5552099099099099</v>
+        <v>0.4784</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H89" s="15" t="n">
-        <v>-122</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H89" s="15" t="n"/>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
         <v/>
@@ -15020,7 +15088,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15037,7 +15105,7 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
@@ -15052,18 +15120,16 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4448198198198199</v>
+        <v>0.5216</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>125</v>
-      </c>
-      <c r="H90" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>-109</v>
+      </c>
+      <c r="H90" s="15" t="n"/>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
         <v/>
@@ -15086,7 +15152,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15103,12 +15169,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -15118,16 +15184,18 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4343</v>
+        <v>0.552110599078341</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="H91" s="15" t="n"/>
+        <v>-123</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>-117</v>
+      </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
         <v/>
@@ -15150,7 +15218,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15167,12 +15235,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -15182,16 +15250,18 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5657</v>
+        <v>0.4478828828828829</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-130</v>
-      </c>
-      <c r="H92" s="15" t="n"/>
+        <v>123</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
         <v/>
@@ -15214,7 +15284,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15231,12 +15301,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -15246,14 +15316,14 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.4335</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="13">
@@ -15278,7 +15348,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15295,12 +15365,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15310,14 +15380,14 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5665</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-115</v>
+        <v>-131</v>
       </c>
       <c r="H94" s="15" t="n"/>
       <c r="I94" s="13">
@@ -15342,7 +15412,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15359,12 +15429,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -15374,14 +15444,14 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4125</v>
+        <v>0.4645</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
@@ -15406,7 +15476,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15423,12 +15493,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -15438,14 +15508,14 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5875</v>
+        <v>0.5355</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-142</v>
+        <v>-115</v>
       </c>
       <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
@@ -15470,7 +15540,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15487,12 +15557,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -15502,18 +15572,16 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5735135135135137</v>
+        <v>0.4125</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H97" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H97" s="15" t="n"/>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
         <v/>
@@ -15536,7 +15604,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -134). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15553,12 +15621,12 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -15568,14 +15636,14 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4265</v>
+        <v>0.5875</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>134</v>
+        <v>-142</v>
       </c>
       <c r="H98" s="15" t="n"/>
       <c r="I98" s="13">
@@ -15600,7 +15668,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +134). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15609,9 +15677,139 @@
         <v/>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>0.5735135135135137</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I99" s="13">
+        <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="16">
+        <f>IF($H$99="","",$F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>IF($H$99="","",MAX(0,($F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))/IF($H$99&lt;0,-100/$H$99,$H$99/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L99" s="18">
+        <f>IF($H$99="","",ROUND(MIN($K$99,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M99" s="12">
+        <f>IF($J$99="","",IF($J$99&lt;0,"Pass",IF($J$99&lt;'Settings'!$B$4,"Thin",IF($J$99&lt;0.06,"✅ Sharp band",IF($J$99&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N99" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.4% (fair -134). Your call.</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="n"/>
+      <c r="P99" s="16">
+        <f>IF(OR($H$99="",$O$99=""),"",(1+IF($H$99&lt;0,-100/$H$99,$H$99/100))/(1+IF($O$99&lt;0,-100/$O$99,$O$99/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="G100" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="H100" s="15" t="n"/>
+      <c r="I100" s="13">
+        <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="16">
+        <f>IF($H$100="","",$F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF($H$100="","",MAX(0,($F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))/IF($H$100&lt;0,-100/$H$100,$H$100/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L100" s="18">
+        <f>IF($H$100="","",ROUND(MIN($K$100,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M100" s="12">
+        <f>IF($J$100="","",IF($J$100&lt;0,"Pass",IF($J$100&lt;'Settings'!$B$4,"Thin",IF($J$100&lt;0.06,"✅ Sharp band",IF($J$100&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.6% (fair +134). Your call.</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="16">
+        <f>IF(OR($H$100="",$O$100=""),"",(1+IF($H$100&lt;0,-100/$H$100,$H$100/100))/(1+IF($O$100&lt;0,-100/$O$100,$O$100/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J98">
+  <conditionalFormatting sqref="J5:J100">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-07-04.xlsx
+++ b/data/output/workbook/2026-07-04.xlsx
@@ -370,7 +370,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10048875"/>
+    <ext cx="10125075" cy="10439400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -400,7 +400,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10525125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -460,7 +460,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10029825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10801350"/>
+    <ext cx="10125075" cy="10544175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04 13:13</t>
+          <t>2026-07-04 15:11</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,170 +1174,320 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays offense vs Seattle Mariners defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E65" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I65" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J65" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L65" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M65" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N65" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O65" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P65" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q65" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays offense vs Seattle Mariners defense</t>
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>4.068</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>4.057</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B67" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C67" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D67" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E67" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F67" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G67" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H67" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I67" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J67" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K67" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L67" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M67" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N67" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O67" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P67" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q67" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>7.979</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>4.068</v>
+        <v>0.915</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>24th</t>
+        <v>1</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.3</v>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>4.033</v>
+        <v>1</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>4.057</v>
+        <v>0.958</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.468</v>
+        <v>7.298</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>9.5</v>
+        <v>6.75</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -1391,390 +1541,390 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>3.25</v>
+        <v>10.25</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>7.979</v>
+        <v>8.333</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.915</v>
+        <v>0.438</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>0.4</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>0.958</v>
+        <v>0.419</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>7.298</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H72" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>Seattle Mariners offense vs Toronto Blue Jays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E73" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I73" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J73" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K73" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L73" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M73" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N73" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O73" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P73" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q73" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
-        <is>
-          <t>Seattle Mariners offense vs Toronto Blue Jays defense</t>
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>3.897</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>4.432</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B75" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C75" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D75" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E75" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F75" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G75" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H75" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I75" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J75" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K75" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L75" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M75" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N75" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O75" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P75" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q75" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>7.894</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>3.897</v>
+        <v>1.312</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
+        <v>2.75</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>4.65</v>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>5.067</v>
+        <v>1.25</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>4.432</v>
+        <v>0.979</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.854</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>8.75</v>
+        <v>7.25</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -1828,221 +1978,71 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>7.894</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.312</v>
+        <v>0.473</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>0.9</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>0.979</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>8.646000000000001</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>9.489000000000001</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D80" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E80" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F80" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G80" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L80" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M80" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="N80" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4785,7 +4785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4802,174 +4802,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.816</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.64</v>
+        <v>1.109</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>4.767</v>
+        <v>0.333</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.816</v>
+        <v>1.354</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.826</v>
+        <v>8.196</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -5023,390 +5173,390 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>6.333</v>
+        <v>6.667</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.109</v>
+        <v>0.556</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.767</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.1</v>
       </c>
       <c r="O73" s="32" t="n">
         <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.354</v>
+        <v>0.44</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C74" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>5.263</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="P78" s="32" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>5.263</v>
+        <v>1.104</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
+        <v>0.667</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.1</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>4.467</v>
+        <v>0.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.52</v>
+        <v>1.043</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>7.667</v>
+        <v>7</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -5460,225 +5610,75 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>7.739</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.104</v>
+        <v>0.453</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.043</v>
+        <v>0.597</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6605,7 +6605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6622,324 +6622,174 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>San Francisco Giants offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="G67" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H67" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N65" s="30" t="inlineStr">
+      <c r="N67" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O65" s="30" t="inlineStr">
+      <c r="O67" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="P67" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>4.114</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>5.641</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>9.239000000000001</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>0.978</v>
+        <v>4.114</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.733</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>5.65</v>
       </c>
       <c r="O68" s="32" t="n">
-        <v>1.333</v>
+        <v>6.5</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>1.24</v>
+        <v>5.641</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>7.587</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>9.5</v>
+        <v>12.25</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -6993,394 +6843,394 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>7.333</v>
+        <v>14</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>7.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.587</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
+      <c r="B72" s="32" t="n">
         <v>0.347</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="E70" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="F70" s="32" t="n">
+      <c r="F72" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G72" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="35" t="inlineStr">
+      <c r="H72" s="35" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K70" s="32" t="n">
+      <c r="K72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L70" s="32" t="n">
+      <c r="L72" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M70" s="32" t="n">
+      <c r="M72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N70" s="32" t="n">
+      <c r="N72" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="O70" s="32" t="n">
+      <c r="O72" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P70" s="32" t="n">
+      <c r="P72" s="32" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="Q70" s="34" t="inlineStr">
+      <c r="Q72" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs San Francisco Giants defense</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F75" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G73" s="30" t="inlineStr">
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H73" s="30" t="inlineStr">
+      <c r="H75" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I73" s="30" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J73" s="30" t="inlineStr">
+      <c r="J75" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K73" s="30" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L73" s="30" t="inlineStr">
+      <c r="L75" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M73" s="30" t="inlineStr">
+      <c r="M75" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N73" s="30" t="inlineStr">
+      <c r="N75" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O73" s="30" t="inlineStr">
+      <c r="O75" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P73" s="30" t="inlineStr">
+      <c r="P75" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q73" s="30" t="inlineStr">
+      <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>6.233</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>6.267</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>4.975</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>8.651999999999999</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>0.92</v>
+        <v>4.91</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6.233</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.75</v>
       </c>
       <c r="O76" s="32" t="n">
-        <v>0.75</v>
+        <v>5.1</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>0.978</v>
+        <v>4.975</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>8.92</v>
+        <v>8.32</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>9.667</v>
+        <v>10.667</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -7434,75 +7284,225 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>7.25</v>
+        <v>13.5</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.173999999999999</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B78" s="32" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.506</v>
       </c>
-      <c r="C78" s="32" t="n">
+      <c r="C80" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D78" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E78" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F78" s="32" t="n">
+      <c r="F80" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G78" s="32" t="n">
+      <c r="G80" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H78" s="33" t="inlineStr">
+      <c r="H80" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J78" s="35" t="inlineStr">
+      <c r="J80" s="35" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="K78" s="32" t="n">
+      <c r="K80" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="L78" s="32" t="n">
+      <c r="L80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M78" s="32" t="n">
+      <c r="M80" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N78" s="32" t="n">
+      <c r="N80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O78" s="32" t="n">
+      <c r="O80" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P78" s="32" t="n">
+      <c r="P80" s="32" t="n">
         <v>0.569</v>
       </c>
-      <c r="Q78" s="34" t="inlineStr">
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6960071942446042</v>
+        <v>0.6967985611510791</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>178</v>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -229). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7809,13 +7809,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5734893617021277</v>
+        <v>0.5734782608695652</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-134</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7856,32 +7856,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6171962616822431</v>
+        <v>0.5524782608695652</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-161</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7922,32 +7922,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5525</v>
+        <v>0.6209428571428571</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-123</v>
+        <v>-164</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>128</v>
+        <v>-103</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8003,17 +8003,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6167465346534653</v>
+        <v>0.6083582089552239</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8069,17 +8069,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6100306930693069</v>
+        <v>0.5779611940298507</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-156</v>
+        <v>-137</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8115,7 +8115,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -8125,27 +8125,27 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5805882352941177</v>
+        <v>0.5970634615384615</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-138</v>
+        <v>-148</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8205,13 +8205,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6182566210045661</v>
+        <v>0.6178761467889908</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5407211538461538</v>
+        <v>0.5400480769230769</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>108</v>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8337,13 +8337,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4586475409836065</v>
+        <v>0.468412017167382</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.8% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8379,37 +8379,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5947372093023255</v>
+        <v>0.5019354838709678</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-147</v>
+        <v>-101</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-115</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8450,32 +8450,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4986635944700461</v>
+        <v>0.5199999999999999</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>101</v>
+        <v>-108</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4834684684684685</v>
+        <v>0.4827027027027028</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>107</v>
@@ -8577,37 +8577,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4262</v>
+        <v>0.4134883720930232</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4161328124999999</v>
+        <v>0.4421666666666667</v>
       </c>
       <c r="G19" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>140</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>156</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4343032786885246</v>
+        <v>0.4334836065573771</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>144</v>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8775,37 +8775,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4501276595744681</v>
+        <v>0.5380470588235293</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>122</v>
+        <v>-116</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>135</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8841,7 +8841,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -8856,22 +8856,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4437394957983193</v>
+        <v>0.5498952380952381</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>125</v>
+        <v>-122</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>138</v>
+        <v>-110</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8907,37 +8907,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5380470588235293</v>
+        <v>0.5229</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-116</v>
+        <v>-110</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8978,32 +8978,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5398536585365854</v>
+        <v>0.4707207207207207</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-117</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-105</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5229</v>
+        <v>0.4535652173913043</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4707207207207207</v>
+        <v>0.5113235294117646</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>112</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9171,17 +9171,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Under 13</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.544395238095238</v>
+        <v>0.5161386138613862</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-119</v>
+        <v>-107</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-110</v>
+        <v>102</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9237,37 +9237,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5134158415841583</v>
+        <v>0.433375</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>131</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9303,17 +9303,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6096510204081632</v>
+        <v>0.5887390557939914</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-156</v>
+        <v>-143</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-145</v>
+        <v>-133</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9534,10 +9534,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5788918032786885</v>
+        <v>0.5808983606557376</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-137</v>
+        <v>-139</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-144</v>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4211065573770492</v>
+        <v>0.4190983606557377</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>144</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4566</v>
+        <v>0.4514</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>113</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9732,10 +9732,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5486</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>125</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9798,13 +9798,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4437394957983193</v>
+        <v>0.4421666666666667</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5562771784232364</v>
+        <v>0.5577983402489626</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-125</v>
+        <v>-126</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-141</v>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9926,17 +9926,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 11</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4236</v>
+        <v>0.3363</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 33.6% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9992,17 +9992,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5764</v>
+        <v>0.6637</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-136</v>
+        <v>-197</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>-102</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 66.4% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10062,13 +10062,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3832352941176471</v>
+        <v>0.379063829787234</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6167465346534653</v>
+        <v>0.6209428571428571</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-161</v>
+        <v>-164</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10326,13 +10326,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5843</v>
+        <v>0.5199999999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-141</v>
+        <v>-108</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10392,13 +10392,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4157</v>
+        <v>0.4800313725490196</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +141). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10458,13 +10458,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.40728</v>
+        <v>0.4083400809716599</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.59274</v>
+        <v>0.5916600000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-146</v>
+        <v>-145</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-150</v>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.48655</v>
+        <v>0.48385</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>100</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10656,10 +10656,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5134158415841583</v>
+        <v>0.5161386138613862</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>102</v>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4193852459016394</v>
+        <v>0.4220491803278689</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>144</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +138). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10788,13 +10788,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5805882352941177</v>
+        <v>0.5779611940298507</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-138</v>
+        <v>-137</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>-101</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10854,10 +10854,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4986635944700461</v>
+        <v>0.5019354838709678</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10920,13 +10920,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5013561085972851</v>
+        <v>0.4980357798165138</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-121</v>
+        <v>-118</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10986,13 +10986,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.513</v>
+        <v>0.5108</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.487</v>
+        <v>0.4892</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>100</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3040074906367041</v>
+        <v>0.3031851851851852</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 30.4% (fair +229). Your call.</t>
+          <t>Model 30.3% (fair +230). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6960071942446042</v>
+        <v>0.6967985611510791</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>178</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -229). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.503890099009901</v>
+        <v>0.5088658536585366</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4961</v>
+        <v>0.4911764705882353</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11382,10 +11382,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5893</v>
+        <v>0.6083</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-143</v>
+        <v>-155</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>122</v>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11448,10 +11448,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4107</v>
+        <v>0.3917</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>103</v>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11514,13 +11514,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4506140350877193</v>
+        <v>0.4473478260869565</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11580,13 +11580,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5493913043478261</v>
+        <v>0.5526635193133047</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11646,10 +11646,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5237725490196079</v>
+        <v>0.5123529411764705</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>-104</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4762254901960785</v>
+        <v>0.4876470588235294</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>104</v>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3817490494296578</v>
+        <v>0.3821673003802282</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>162</v>
@@ -11844,13 +11844,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6182566210045661</v>
+        <v>0.6178761467889908</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4343032786885246</v>
+        <v>0.4334836065573771</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>144</v>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5657311475409836</v>
+        <v>0.5665153846153846</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.6092</v>
+        <v>0.6087</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>-156</v>
@@ -12108,13 +12108,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.3908</v>
+        <v>0.3913</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>156</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3899590163934427</v>
+        <v>0.3916393442622951</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>144</v>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12240,13 +12240,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6100306930693069</v>
+        <v>0.6083582089552239</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-156</v>
+        <v>-155</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12306,13 +12306,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4161328124999999</v>
+        <v>0.4134883720930232</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12372,13 +12372,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5838421874999999</v>
+        <v>0.5865230769230769</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-156</v>
+        <v>-160</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12438,10 +12438,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3976</v>
+        <v>0.3542</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>117</v>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +152). Your call.</t>
+          <t>Model 35.4% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6024</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-152</v>
+        <v>-182</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>115</v>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -152). Your call.</t>
+          <t>Model 64.6% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12570,13 +12570,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3828070175438596</v>
+        <v>0.4112875536480687</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12636,13 +12636,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6171962616822431</v>
+        <v>0.5887390557939914</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-161</v>
+        <v>-143</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>114</v>
+        <v>-133</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12830,10 +12830,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5984852459016393</v>
+        <v>0.5952393442622951</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>-144</v>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12896,13 +12896,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4015384615384616</v>
+        <v>0.4047520661157025</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13094,13 +13094,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5525</v>
+        <v>0.5524782608695652</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13356,10 +13356,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.545</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.455</v>
+        <v>0.4521</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6875</v>
+        <v>0.6928</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-220</v>
+        <v>-226</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 68.8% (fair -220). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13548,10 +13548,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3125</v>
+        <v>0.3071</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 31.2% (fair +220). Your call.</t>
+          <t>Model 30.7% (fair +226). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4197</v>
+        <v>0.4227</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13676,10 +13676,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5803</v>
+        <v>0.5773</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-138</v>
+        <v>-137</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4834684684684685</v>
+        <v>0.4827027027027028</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>107</v>
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5165253456221198</v>
+        <v>0.5172801843317972</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>-107</v>
@@ -13872,13 +13872,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.460106976744186</v>
+        <v>0.3297</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-115</v>
+        <v>144</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 33.0% (fair +203). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13938,13 +13938,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5398536585365854</v>
+        <v>0.6703</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-117</v>
+        <v>-203</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14004,13 +14004,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.36524</v>
+        <v>0.3578039215686274</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14070,13 +14070,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.6347571428571429</v>
+        <v>0.6422</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-174</v>
+        <v>-179</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-180</v>
+        <v>-190</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14136,13 +14136,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5343361502347418</v>
+        <v>0.4886853658536585</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-115</v>
+        <v>105</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-113</v>
+        <v>-105</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14202,13 +14202,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.465625</v>
+        <v>0.5113235294117646</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>115</v>
+        <v>-105</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14264,14 +14264,14 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Over 11</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4948952380952381</v>
+        <v>0.470852380952381</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>-110</v>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14330,14 +14330,14 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5051095238095238</v>
+        <v>0.5291523809523809</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-110</v>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14400,13 +14400,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5766607843137256</v>
+        <v>0.6359142857142857</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-136</v>
+        <v>-175</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-155</v>
+        <v>-180</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14466,13 +14466,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4233478260869565</v>
+        <v>0.36408</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14532,10 +14532,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5407211538461538</v>
+        <v>0.5400480769230769</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>108</v>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14598,10 +14598,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4593</v>
+        <v>0.45995</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>100</v>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14664,10 +14664,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5058952380952381</v>
+        <v>0.4911238095238095</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-102</v>
+        <v>104</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>-110</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14730,10 +14730,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4941095238095238</v>
+        <v>0.5088809523809523</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>-110</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14796,13 +14796,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5738142857142857</v>
+        <v>0.5666037735849058</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-135</v>
+        <v>-131</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-180</v>
+        <v>-165</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14862,13 +14862,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4262</v>
+        <v>0.433375</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14928,13 +14928,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4586475409836065</v>
+        <v>0.468412017167382</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.8% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14994,13 +14994,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5413890756302521</v>
+        <v>0.5316004291845494</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.2% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15056,17 +15056,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5074142857142857</v>
+        <v>0.4500921658986176</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-103</v>
+        <v>122</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-110</v>
+        <v>117</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15122,14 +15122,14 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4925904761904762</v>
+        <v>0.5498952380952381</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>103</v>
+        <v>-122</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-110</v>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15192,13 +15192,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3903913043478262</v>
+        <v>0.3974545454545454</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15258,10 +15258,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.6096510204081632</v>
+        <v>0.6025489795918367</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-156</v>
+        <v>-152</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-145</v>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15324,13 +15324,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4501276595744681</v>
+        <v>0.4535652173913043</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15390,10 +15390,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5498665236051502</v>
+        <v>0.5464416309012876</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-133</v>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4090222222222222</v>
+        <v>0.4034782608695653</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15654,13 +15654,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5910000000000001</v>
+        <v>0.5965372549019609</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-144</v>
+        <v>-148</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15980,17 +15980,17 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5113243902439024</v>
+        <v>0.5524</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-105</v>
+        <v>-123</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-105</v>
+        <v>156</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16046,17 +16046,17 @@
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4886697674418605</v>
+        <v>0.4476</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16772,17 +16772,17 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4925380952380952</v>
+        <v>0.5336181818181818</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>103</v>
+        <v>-114</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -16838,17 +16838,17 @@
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5074666666666666</v>
+        <v>0.46635</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-103</v>
+        <v>114</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -16908,13 +16908,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5909074074074073</v>
+        <v>0.5957636363636364</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-170</v>
+        <v>-175</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4090833333333334</v>
+        <v>0.404204081632653</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4768</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H119" s="15" t="n"/>
       <c r="I119" s="13">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17104,10 +17104,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5216</v>
+        <v>0.5232</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H120" s="15" t="n"/>
       <c r="I120" s="13">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17164,17 +17164,17 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Over 13</t>
+          <t>Over 13.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4556095238095238</v>
+        <v>0.3158</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-110</v>
+        <v>150</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 31.6% (fair +217). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17230,14 +17230,14 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Under 13</t>
+          <t>Under 13.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.544395238095238</v>
+        <v>0.6841999999999999</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-119</v>
+        <v>-217</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>-110</v>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 68.4% (fair -217). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5830416666666667</v>
+        <v>0.584325</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>-140</v>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17366,10 +17366,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4169767441860465</v>
+        <v>0.4156279069767442</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>115</v>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 41.6% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17432,10 +17432,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5452092165898618</v>
+        <v>0.5484442396313365</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>-117</v>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17498,10 +17498,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4547465437788019</v>
+        <v>0.4515668202764977</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>117</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17560,17 +17560,17 @@
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4653804878048781</v>
+        <v>0.4852450980392157</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -17626,17 +17626,17 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5346162790697675</v>
+        <v>0.5147134615384615</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-115</v>
+        <v>-106</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -17660,7 +17660,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -17696,10 +17696,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5822529411764706</v>
+        <v>0.5775117647058824</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-139</v>
+        <v>-137</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>-155</v>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4177391304347826</v>
+        <v>0.4225217391304348</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>130</v>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4375</v>
+        <v>0.4335</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H131" s="15" t="n"/>
       <c r="I131" s="13">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +129). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5625</v>
+        <v>0.5665</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-129</v>
+        <v>-131</v>
       </c>
       <c r="H132" s="15" t="n"/>
       <c r="I132" s="13">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -129). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18080,17 +18080,17 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4052487804878049</v>
+        <v>0.4029411764705882</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H135" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -18146,17 +18146,17 @@
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5947372093023255</v>
+        <v>0.5970634615384615</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -18216,7 +18216,7 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.4129</v>
+        <v>0.4125</v>
       </c>
       <c r="G137" s="14" t="n">
         <v>142</v>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.5871</v>
+        <v>0.5875</v>
       </c>
       <c r="G138" s="14" t="n">
         <v>-142</v>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18344,13 +18344,13 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5734893617021277</v>
+        <v>0.5734782608695652</v>
       </c>
       <c r="G139" s="14" t="n">
         <v>-134</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -18685,28 +18685,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2499</v>
+        <v>0.2497</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4475</v>
+        <v>0.4455</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-7.22</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-3.3</v>
+        <v>-3.74</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.4923</v>
+        <v>0.4949</v>
       </c>
     </row>
     <row r="6">
@@ -18716,28 +18716,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2514</v>
+        <v>0.2512</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.4586</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-4.57</v>
+        <v>-5.57</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-2.54</v>
+        <v>-3.08</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5091</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="7">
@@ -18820,7 +18820,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=284, ECE 0.051 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=285, ECE 0.050 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -18915,16 +18915,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4586</v>
+        <v>0.4583</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4725</v>
+        <v>0.4674</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.0139</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -20051,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20068,174 +20068,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs New York Yankees defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>3.744</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.776</v>
+        <v>1.061</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>5.933</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.65</v>
+        <v>1</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>4.633</v>
+        <v>2</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>3.744</v>
+        <v>0.913</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.776</v>
+        <v>8.939</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>8.667</v>
+        <v>8</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -20289,394 +20439,394 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>10.667</v>
+        <v>9.667</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.609</v>
+        <v>8.435</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.061</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="C73" s="32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F73" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.6</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.913</v>
+        <v>0.479</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.939</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.435</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Minnesota Twins defense</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.744</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>5.132</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.109</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.744</v>
+        <v>1.413</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>0.333</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.6</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.767</v>
+        <v>1.667</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.132</v>
+        <v>0.918</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.109</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>8.333</v>
+        <v>9.667</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -20730,221 +20880,71 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>9</v>
+        <v>11.667</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.413</v>
+        <v>0.63</v>
       </c>
       <c r="C81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D81" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.5</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>1.667</v>
+        <v>0.633</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.918</v>
+        <v>0.605</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>11.667</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>8.265000000000001</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-04.xlsx
+++ b/data/output/workbook/2026-07-04.xlsx
@@ -429,7 +429,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10801350"/>
+    <ext cx="10125075" cy="10572750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -579,7 +579,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04 19:01</t>
+          <t>2026-07-04 20:02</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3897,320 +3897,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.908</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>4.127</v>
-      </c>
-      <c r="Q69" s="33" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q70" s="33" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.354</v>
+        <v>4.908</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.067</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>1</v>
+        <v>4.367</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.143</v>
+        <v>4.127</v>
       </c>
       <c r="Q71" s="33" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>9.208</v>
+        <v>7.792</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -4264,390 +4114,390 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>10</v>
+        <v>10.333</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q73" s="33" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q74" s="33" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.581</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="32" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.133</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.367</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.355</v>
       </c>
-      <c r="Q73" s="33" t="inlineStr">
+      <c r="Q75" s="33" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>3.949</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.724</v>
-      </c>
-      <c r="Q77" s="33" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="Q78" s="33" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>0.959</v>
+        <v>3.949</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.7</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.35</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>0.5</v>
+        <v>4.333</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.062</v>
+        <v>4.724</v>
       </c>
       <c r="Q79" s="33" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>12.667</v>
+        <v>9.667</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -4701,71 +4551,221 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.938</v>
+        <v>7.854</v>
       </c>
       <c r="Q80" s="33" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q81" s="33" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q82" s="33" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.233</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H81" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="32" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="32" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.541</v>
       </c>
-      <c r="Q81" s="33" t="inlineStr">
+      <c r="Q83" s="33" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4784,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4801,249 +4801,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.816</v>
-      </c>
-      <c r="Q70" s="33" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.826</v>
+        <v>4.64</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.167</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H71" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.6</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>6.333</v>
+        <v>4.767</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.896</v>
+        <v>4.816</v>
       </c>
       <c r="Q71" s="33" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.109</v>
+        <v>7.826</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>0.5</v>
+        <v>7.75</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5097,28 +5022,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>0.333</v>
+        <v>6.333</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.354</v>
+        <v>7.896</v>
       </c>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.196</v>
+        <v>1.109</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5172,315 +5097,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>6.667</v>
+        <v>0.333</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.708</v>
+        <v>1.354</v>
       </c>
       <c r="Q73" s="33" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q74" s="33" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.556</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.767</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.133</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.44</v>
       </c>
-      <c r="Q74" s="33" t="inlineStr">
+      <c r="Q75" s="33" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.263</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="Q78" s="33" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>5.263</v>
       </c>
       <c r="C79" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="E79" s="31" t="n">
         <v>7.667</v>
       </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F79" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.1</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>9</v>
+        <v>4.467</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>4.52</v>
       </c>
       <c r="Q79" s="33" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.104</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>0.667</v>
+        <v>7.667</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -5534,28 +5459,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.043</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q80" s="33" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.458</v>
+        <v>1.104</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>7</v>
+        <v>0.667</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -5609,75 +5534,150 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>8.75</v>
+        <v>0.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.739</v>
+        <v>1.043</v>
       </c>
       <c r="Q81" s="33" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="Q82" s="33" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.453</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="32" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="J83" s="34" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.597</v>
       </c>
-      <c r="Q82" s="33" t="inlineStr">
+      <c r="Q83" s="33" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7808,13 +7808,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.744453125</v>
+        <v>0.7444573643410852</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-291</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6735185185185185</v>
+        <v>0.6732592592592592</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-206</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 67.4% (fair -206). Your call.</t>
+          <t>Model 67.3% (fair -206). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7940,13 +7940,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6185454545454545</v>
+        <v>0.6178070175438596</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7987,32 +7987,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5734893617021277</v>
+        <v>0.5744672131147541</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-134</v>
+        <v>-135</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8048,37 +8048,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6522995073891626</v>
+        <v>0.569404255319149</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-188</v>
+        <v>-132</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-103</v>
+        <v>135</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.2% (fair -188). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8119,32 +8119,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5554222222222223</v>
+        <v>0.6522995073891626</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-125</v>
+        <v>-188</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>125</v>
+        <v>-103</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 65.2% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8185,32 +8185,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6083663366336634</v>
+        <v>0.552511013215859</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-155</v>
+        <v>-123</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 55.3% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8266,17 +8266,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.56385</v>
+        <v>0.6135467980295566</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-129</v>
+        <v>-159</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8336,13 +8336,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6178410714285715</v>
+        <v>0.6175380090497737</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-162</v>
+        <v>-161</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-124</v>
+        <v>-121</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8378,37 +8378,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.544264705882353</v>
+        <v>0.4634854771784232</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-119</v>
+        <v>116</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4754935622317596</v>
+        <v>0.4763948497854077</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>110</v>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8510,17 +8510,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8530,17 +8530,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4568333333333334</v>
+        <v>0.5411274509803922</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>119</v>
+        <v>-118</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8576,37 +8576,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5624174757281554</v>
+        <v>0.4568333333333334</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-129</v>
+        <v>119</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-106</v>
+        <v>140</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -129). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8666,13 +8666,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4011029411764706</v>
+        <v>0.3980656934306569</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8779,32 +8779,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.42844</v>
+        <v>0.5105164319248826</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8840,37 +8840,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4033840304182509</v>
+        <v>0.4244664031620553</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8906,37 +8906,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5523047619047619</v>
+        <v>0.5365</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-123</v>
+        <v>-116</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8977,32 +8977,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.447404255319149</v>
+        <v>0.5509038461538461</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>124</v>
+        <v>-123</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>135</v>
+        <v>-108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9043,32 +9043,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4361410788381742</v>
+        <v>0.497887323943662</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -9119,22 +9119,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4726576576576577</v>
+        <v>0.4025855513307985</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9190,17 +9190,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5346313725490196</v>
+        <v>0.447404255319149</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-115</v>
+        <v>124</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-104</v>
+        <v>135</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9241,32 +9241,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4912206572769953</v>
+        <v>0.5620023255813954</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>104</v>
+        <v>-128</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>113</v>
+        <v>-115</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9307,32 +9307,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Under 13.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5463857142857143</v>
+        <v>0.4931924882629108</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-120</v>
+        <v>103</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9389,7 +9389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5270209302325581</v>
+        <v>0.5314069767441861</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-115</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4729577464788733</v>
+        <v>0.4685915492957747</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>113</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.579</v>
+        <v>0.5772</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-138</v>
+        <v>-137</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>100</v>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.421</v>
+        <v>0.4228</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>114</v>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.39972</v>
+        <v>0.39236</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>150</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.60762</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-150</v>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10589,10 +10589,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4575</v>
+        <v>0.4712</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>100</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +119). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10655,10 +10655,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5425</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-119</v>
+        <v>-112</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>127</v>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4361410788381742</v>
+        <v>0.4634854771784232</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>141</v>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.56385</v>
+        <v>0.5365</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-129</v>
+        <v>-116</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>100</v>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10991,7 +10991,7 @@
         <v>129</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11057,7 +11057,7 @@
         <v>-129</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11117,13 +11117,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3040074906367041</v>
+        <v>0.3039923954372624</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>229</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4911165048543689</v>
+        <v>0.4912135922330097</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>104</v>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5088980769230769</v>
+        <v>0.5087942307692307</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-104</v>
@@ -11381,13 +11381,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5765</v>
+        <v>0.6294</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-136</v>
+        <v>-170</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11447,13 +11447,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4235</v>
+        <v>0.3706</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11513,13 +11513,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4540888888888889</v>
+        <v>0.4533480176211453</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11579,10 +11579,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5459321585903084</v>
+        <v>0.5466594713656387</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-127</v>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11645,10 +11645,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5171</v>
+        <v>0.497887323943662</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-107</v>
+        <v>101</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>113</v>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11711,13 +11711,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4829</v>
+        <v>0.5020953488372093</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>107</v>
+        <v>-101</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>117</v>
+        <v>-115</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11777,10 +11777,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3821348314606742</v>
+        <v>0.3824344569288389</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>167</v>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 38.2% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11843,13 +11843,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6178410714285715</v>
+        <v>0.6175380090497737</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-162</v>
+        <v>-161</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-124</v>
+        <v>-121</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11909,13 +11909,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.42844</v>
+        <v>0.4244664031620553</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11975,13 +11975,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5715600000000001</v>
+        <v>0.5755546875000001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12041,10 +12041,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.6087</v>
+        <v>0.5955</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-156</v>
+        <v>-147</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>117</v>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12107,10 +12107,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.3913</v>
+        <v>0.4045</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>117</v>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3916393442622951</v>
+        <v>0.3864705882352941</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12239,13 +12239,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6083663366336634</v>
+        <v>0.6135467980295566</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-155</v>
+        <v>-159</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12305,13 +12305,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4011029411764706</v>
+        <v>0.3980656934306569</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5989037037037037</v>
+        <v>0.6019710144927535</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-170</v>
+        <v>-176</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12437,13 +12437,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3781</v>
+        <v>0.3705</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +164). Your call.</t>
+          <t>Model 37.0% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12503,13 +12503,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6219</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-164</v>
+        <v>-170</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -164). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3814414414414415</v>
+        <v>0.3822072072072072</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>162</v>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12635,13 +12635,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6185454545454545</v>
+        <v>0.6178070175438596</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>-162</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.497</v>
+        <v>0.4964</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>101</v>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.503</v>
+        <v>0.5036</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-101</v>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12829,13 +12829,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5912053941908713</v>
+        <v>0.5986241935483871</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-145</v>
+        <v>-149</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-141</v>
+        <v>-148</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4087916666666667</v>
+        <v>0.4013934426229508</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12961,10 +12961,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4311</v>
+        <v>0.4277</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>122</v>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13027,13 +13027,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5689</v>
+        <v>0.5723</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13093,13 +13093,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5554222222222223</v>
+        <v>0.552511013215859</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-125</v>
+        <v>-123</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.3% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13159,10 +13159,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4446</v>
+        <v>0.4475</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13223,10 +13223,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.6018</v>
+        <v>0.5105164319248826</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-151</v>
+        <v>-104</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>113</v>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13289,13 +13289,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3982</v>
+        <v>0.4894720930232558</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>117</v>
+        <v>-115</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.545</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.455</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6928</v>
+        <v>0.6875</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-226</v>
+        <v>-220</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 68.8% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3071</v>
+        <v>0.3125</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 30.7% (fair +226). Your call.</t>
+          <t>Model 31.2% (fair +220). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13739,10 +13739,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4912206572769953</v>
+        <v>0.4931924882629108</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>113</v>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13805,13 +13805,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5087351851851852</v>
+        <v>0.5068023474178404</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13871,13 +13871,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4376056338028169</v>
+        <v>0.3628</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +129). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13937,13 +13937,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5624174757281554</v>
+        <v>0.6372</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-129</v>
+        <v>-176</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-106</v>
+        <v>102</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -129). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.3265185185185185</v>
+        <v>0.3267407407407407</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>206</v>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.6735185185185185</v>
+        <v>0.6732592592592592</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>-206</v>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 67.4% (fair -206). Your call.</t>
+          <t>Model 67.3% (fair -206). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14135,13 +14135,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4888</v>
+        <v>0.4610138248847926</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14201,13 +14201,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5111764705882352</v>
+        <v>0.5389615384615385</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-105</v>
+        <v>-117</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14231,7 +14231,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14263,17 +14263,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.470852380952381</v>
+        <v>0.386</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-110</v>
+        <v>178</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14329,17 +14329,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5291523809523809</v>
+        <v>0.614</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-112</v>
+        <v>-159</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14395,17 +14395,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.6251592592592592</v>
+        <v>0.4255691056910569</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-167</v>
+        <v>135</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-170</v>
+        <v>146</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14461,17 +14461,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.374875</v>
+        <v>0.5744672131147541</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>167</v>
+        <v>-135</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.544264705882353</v>
+        <v>0.5411274509803922</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>104</v>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14597,13 +14597,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4557</v>
+        <v>0.4588745098039215</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14663,10 +14663,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4962254901960784</v>
+        <v>0.4993627450980392</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>104</v>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14729,13 +14729,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5037882352941176</v>
+        <v>0.50065</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14861,13 +14861,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.744453125</v>
+        <v>0.7444573643410852</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>-291</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4754935622317596</v>
+        <v>0.4763948497854077</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>110</v>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5245044052863437</v>
+        <v>0.5236092511013216</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>-110</v>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15059,13 +15059,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5158418604651164</v>
+        <v>0.5261131455399061</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-107</v>
+        <v>-111</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15125,13 +15125,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4841346153846153</v>
+        <v>0.4738967136150236</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15191,13 +15191,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3561596958174905</v>
+        <v>0.3536329588014981</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.4% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.6438592592592591</v>
+        <v>0.6463777777777777</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-181</v>
+        <v>-183</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-170</v>
@@ -15287,7 +15287,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.6% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15455,10 +15455,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5266274509803921</v>
+        <v>0.5297882352941176</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>-104</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15521,13 +15521,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4733529411764705</v>
+        <v>0.4702</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15587,13 +15587,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.3942213114754098</v>
+        <v>0.39044</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.6057796875</v>
+        <v>0.6095578125</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-154</v>
+        <v>-156</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>-156</v>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15832,32 +15832,32 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.5649347826086957</v>
+        <v>0.5620023255813954</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>-130</v>
+        <v>-115</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15898,32 +15898,32 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.4350660792951542</v>
+        <v>0.438</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -15964,32 +15964,32 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5523047619047619</v>
+        <v>0.4034552845528456</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-123</v>
+        <v>148</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-110</v>
+        <v>146</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16030,32 +16030,32 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4476960784313725</v>
+        <v>0.5965372549019609</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>123</v>
+        <v>-148</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>104</v>
+        <v>-155</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16106,22 +16106,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5607120171673819</v>
+        <v>0.5632757709251101</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16172,22 +16172,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.439304347826087</v>
+        <v>0.4366960352422907</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16211,7 +16211,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16228,32 +16228,32 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5273166666666667</v>
+        <v>0.5509038461538461</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-112</v>
+        <v>-123</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16294,32 +16294,32 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4726576576576577</v>
+        <v>0.4491176470588235</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16360,32 +16360,32 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5242829268292684</v>
+        <v>0.5550609442060086</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-110</v>
+        <v>-125</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-105</v>
+        <v>-133</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16426,32 +16426,32 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4757255813953489</v>
+        <v>0.444954954954955</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-115</v>
+        <v>122</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16502,22 +16502,22 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.6063905660377359</v>
+        <v>0.5251685185185185</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-154</v>
+        <v>-111</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-165</v>
+        <v>-116</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16568,22 +16568,22 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.3935744680851064</v>
+        <v>0.4748401826484018</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -16634,22 +16634,22 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.5346313725490196</v>
+        <v>0.5242829268292684</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -16690,7 +16690,7 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
@@ -16700,22 +16700,22 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4654</v>
+        <v>0.4757255813953489</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>100</v>
+        <v>-115</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -16766,22 +16766,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.5044117647058823</v>
+        <v>0.6006098039215687</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>-102</v>
+        <v>-150</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>104</v>
+        <v>-155</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
@@ -16832,22 +16832,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4956057692307692</v>
+        <v>0.3993965517241378</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-108</v>
+        <v>132</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -16898,22 +16898,22 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers +1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.596637037037037</v>
+        <v>0.5343764705882352</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-148</v>
+        <v>-115</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-170</v>
+        <v>-104</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -16964,22 +16964,22 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4033840304182509</v>
+        <v>0.4656</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17020,31 +17020,33 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4799</v>
+        <v>0.5406</v>
       </c>
       <c r="G119" s="14" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H119" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="H119" s="15" t="n"/>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
         <v/>
@@ -17067,7 +17069,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17084,31 +17086,33 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5201</v>
+        <v>0.4594</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H120" s="15" t="n"/>
+        <v>118</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
         <v/>
@@ -17131,7 +17135,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17148,32 +17152,32 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Over 13.5</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4536235294117647</v>
+        <v>0.5974555555555555</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>120</v>
+        <v>-148</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-104</v>
+        <v>-170</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -17197,7 +17201,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17214,32 +17218,32 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Under 13.5</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5463857142857143</v>
+        <v>0.4025855513307985</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-120</v>
+        <v>148</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-110</v>
+        <v>163</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -17263,7 +17267,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17290,23 +17294,21 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5746</v>
+        <v>0.4799</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-135</v>
-      </c>
-      <c r="H123" s="15" t="n">
-        <v>-130</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="H123" s="15" t="n"/>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
         <v/>
@@ -17329,7 +17331,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17356,23 +17358,21 @@
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4253990610328639</v>
+        <v>0.5201</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>135</v>
-      </c>
-      <c r="H124" s="15" t="n">
-        <v>113</v>
-      </c>
+        <v>-108</v>
+      </c>
+      <c r="H124" s="15" t="n"/>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
         <v/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17431,13 +17431,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5484442396313365</v>
+        <v>0.5471860465116279</v>
       </c>
       <c r="G125" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17497,7 +17497,7 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4515668202764977</v>
+        <v>0.4528110599078342</v>
       </c>
       <c r="G126" s="14" t="n">
         <v>121</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17635,7 +17635,7 @@
         <v>-106</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-110</v>
+        <v>122</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -17676,33 +17676,31 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5847600000000001</v>
+        <v>0.4311</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-141</v>
-      </c>
-      <c r="H129" s="15" t="n">
-        <v>-150</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="H129" s="15" t="n"/>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
         <v/>
@@ -17725,7 +17723,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -17742,33 +17740,31 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4152459016393443</v>
+        <v>0.5689</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>141</v>
-      </c>
-      <c r="H130" s="15" t="n">
-        <v>144</v>
-      </c>
+        <v>-132</v>
+      </c>
+      <c r="H130" s="15" t="n"/>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
         <v/>
@@ -17791,7 +17787,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -17808,12 +17804,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -17823,14 +17819,14 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4311</v>
+        <v>0.4615</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H131" s="15" t="n"/>
       <c r="I131" s="13">
@@ -17855,7 +17851,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -17872,12 +17868,12 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -17887,14 +17883,14 @@
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5689</v>
+        <v>0.5385</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-132</v>
+        <v>-117</v>
       </c>
       <c r="H132" s="15" t="n"/>
       <c r="I132" s="13">
@@ -17919,7 +17915,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -17946,21 +17942,23 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.4631</v>
+        <v>0.2601</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="H133" s="15" t="n"/>
+        <v>284</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
         <v/>
@@ -17983,7 +17981,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 26.0% (fair +284). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -18010,21 +18008,23 @@
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5369</v>
+        <v>0.7399</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>-116</v>
-      </c>
-      <c r="H134" s="15" t="n"/>
+        <v>-284</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
         <v/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 74.0% (fair -284). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -18064,33 +18064,31 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.2604</v>
+        <v>0.4109</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>284</v>
-      </c>
-      <c r="H135" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="H135" s="15" t="n"/>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
         <v/>
@@ -18113,7 +18111,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 26.0% (fair +284). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -18130,33 +18128,31 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.7396</v>
+        <v>0.5891</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-284</v>
-      </c>
-      <c r="H136" s="15" t="n">
-        <v>-110</v>
-      </c>
+        <v>-143</v>
+      </c>
+      <c r="H136" s="15" t="n"/>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
         <v/>
@@ -18179,7 +18175,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 74.0% (fair -284). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -18196,12 +18192,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -18211,16 +18207,18 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.4109</v>
+        <v>0.569404255319149</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>143</v>
-      </c>
-      <c r="H137" s="15" t="n"/>
+        <v>-132</v>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>135</v>
+      </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
         <v/>
@@ -18243,7 +18241,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18260,12 +18258,12 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -18275,14 +18273,14 @@
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.5891</v>
+        <v>0.4306</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>-143</v>
+        <v>132</v>
       </c>
       <c r="H138" s="15" t="n"/>
       <c r="I138" s="13">
@@ -18307,7 +18305,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18334,22 +18332,22 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5734893617021277</v>
+        <v>0.5008823529411764</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-134</v>
+        <v>-100</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>135</v>
+        <v>-104</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -18373,7 +18371,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -18400,21 +18398,23 @@
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4265</v>
+        <v>0.4991</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="H140" s="15" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
         <v/>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +134). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -18446,141 +18446,9 @@
         <v/>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B141" s="12" t="inlineStr">
-        <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>Over 8.5</t>
-        </is>
-      </c>
-      <c r="F141" s="13" t="n">
-        <v>0.4968039215686275</v>
-      </c>
-      <c r="G141" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="H141" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I141" s="13">
-        <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
-        <v/>
-      </c>
-      <c r="J141" s="16">
-        <f>IF($H$141="","",$F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))</f>
-        <v/>
-      </c>
-      <c r="K141" s="17">
-        <f>IF($H$141="","",MAX(0,($F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))/IF($H$141&lt;0,-100/$H$141,$H$141/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L141" s="18">
-        <f>IF($H$141="","",ROUND(MIN($K$141,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M141" s="12">
-        <f>IF($J$141="","",IF($J$141&lt;0,"Pass",IF($J$141&lt;'Settings'!$B$4,"Thin",IF($J$141&lt;0.06,"✅ Sharp band",IF($J$141&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N141" s="19" t="inlineStr">
-        <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
-        </is>
-      </c>
-      <c r="O141" s="15" t="n"/>
-      <c r="P141" s="16">
-        <f>IF(OR($H$141="",$O$141=""),"",(1+IF($H$141&lt;0,-100/$H$141,$H$141/100))/(1+IF($O$141&lt;0,-100/$O$141,$O$141/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B142" s="20" t="inlineStr">
-        <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="C142" s="20" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="D142" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E142" s="20" t="inlineStr">
-        <is>
-          <t>Under 8.5</t>
-        </is>
-      </c>
-      <c r="F142" s="13" t="n">
-        <v>0.5032274509803921</v>
-      </c>
-      <c r="G142" s="14" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H142" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I142" s="13">
-        <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
-        <v/>
-      </c>
-      <c r="J142" s="16">
-        <f>IF($H$142="","",$F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))</f>
-        <v/>
-      </c>
-      <c r="K142" s="17">
-        <f>IF($H$142="","",MAX(0,($F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))/IF($H$142&lt;0,-100/$H$142,$H$142/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L142" s="18">
-        <f>IF($H$142="","",ROUND(MIN($K$142,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M142" s="12">
-        <f>IF($J$142="","",IF($J$142&lt;0,"Pass",IF($J$142&lt;'Settings'!$B$4,"Thin",IF($J$142&lt;0.06,"✅ Sharp band",IF($J$142&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N142" s="19" t="inlineStr">
-        <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
-        </is>
-      </c>
-      <c r="O142" s="15" t="n"/>
-      <c r="P142" s="16">
-        <f>IF(OR($H$142="",$O$142=""),"",(1+IF($H$142&lt;0,-100/$H$142,$H$142/100))/(1+IF($O$142&lt;0,-100/$O$142,$O$142/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J142">
+  <conditionalFormatting sqref="J5:J140">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -20962,7 +20830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20979,170 +20847,320 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Detroit Tigers offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Detroit Tigers offense vs Texas Rangers defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.307</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H69" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="Q69" s="33" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>7.673</v>
+      </c>
+      <c r="Q70" s="33" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.307</v>
+        <v>1.02</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H71" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
+        <v>2.25</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>5.35</v>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.633</v>
+        <v>1</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.169</v>
+        <v>1.163</v>
       </c>
       <c r="Q71" s="33" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.755</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -21196,398 +21214,398 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>8.667</v>
+        <v>12</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.673</v>
+        <v>8.571</v>
       </c>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.02</v>
+        <v>0.547</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="32" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.9</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.163</v>
+        <v>0.776</v>
       </c>
       <c r="Q73" s="33" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>8.571</v>
-      </c>
-      <c r="Q74" s="33" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Detroit Tigers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="Q75" s="33" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Detroit Tigers defense</t>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q77" s="33" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>7.592</v>
+      </c>
+      <c r="Q78" s="33" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.217</v>
+        <v>1.041</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>3.55</v>
+        <v>0</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>3.733</v>
+        <v>1.5</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.04</v>
+        <v>0.898</v>
       </c>
       <c r="Q79" s="33" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>7.816</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9</v>
+        <v>9.333</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -21641,221 +21659,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.592</v>
+        <v>7.776</v>
       </c>
       <c r="Q80" s="33" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.041</v>
+        <v>0.605</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.7</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.2</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>0.898</v>
+        <v>0.36</v>
       </c>
       <c r="Q81" s="33" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>8.592000000000001</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="Q82" s="33" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q83" s="33" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
